--- a/2D视觉/bin/x64/Debug/MODEL/2.xlsx
+++ b/2D视觉/bin/x64/Debug/MODEL/2.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">150</t>
   </si>
   <si>
-    <t xml:space="preserve">300</t>
+    <t xml:space="preserve">2</t>
   </si>
   <si>
     <t xml:space="preserve">True</t>
